--- a/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
@@ -833,7 +833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -958,12 +958,12 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>POWER</t>
+          <t>DIP</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>محور توان افت دارد</t>
+          <t>جریان باتری افت دارد (نقطه‌ای کمتر از قبلی)</t>
         </is>
       </c>
     </row>
@@ -998,6 +998,23 @@
       <c r="C10" s="10" t="inlineStr">
         <is>
           <t>پاک‌کردن، نوشتن یا بازبینی فلش شکست خورد</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t>۸</t>
+        </is>
+      </c>
+      <c r="B11" s="10" t="inlineStr">
+        <is>
+          <t>RANGE</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>شمارش بالاتر از ADC ۱۲ بیتی (۴۰۹۵)</t>
         </is>
       </c>
     </row>

--- a/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
@@ -69,7 +69,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002F5597"/>
+        <fgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
     <fill>
@@ -523,7 +523,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007F7F7F"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -680,7 +680,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -829,7 +829,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002F5597"/>
+    <tabColor rgb="007030A0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
+++ b/Firmware/Modules/CalLut/CalLut_State_Machine.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="۱ مراحل" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="۲ کد وضعیت" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="راهنما" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۱ مراحل" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="۲ کد وضعیت" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -775,7 +775,7 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>اعتبارسنجی، تعلیق شارژر، پاک و نوشتن صفحه، بازخوانی از خود فلش</t>
+          <t>اعتبارسنجی، تعلیق شارژر، پاک و نوشتن صفحه، بازخوانی از خود فلش؛ جدول بدون تغییر هم فعلاً نوشته می‌شود (ایراد باز)</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
